--- a/Leitor_de_Fatura/Faturas_Texter/MIRANDA_Texter/MIRANDA_Analaiser.xlsx
+++ b/Leitor_de_Fatura/Faturas_Texter/MIRANDA_Texter/MIRANDA_Analaiser.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INFORMAÇÃO GERAL" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISTÓRICO DE CONSUMO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="INFORMAÇÃO GERAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="HISTÓRICO DE CONSUMO" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -457,7 +457,8 @@
     <col width="37" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="47" customWidth="1" min="6" max="6"/>
-    <col width="141" customWidth="1" min="7" max="7"/>
+    <col width="172" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -496,6 +497,11 @@
           <t>ENDEREÇO</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>COMPLEMENTO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -530,7 +536,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL CEP: 79380000 MIRANDA MS (AG: 13)</t>
+          <t>PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL CEP: 79380000 MIRANDA MS (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>00000Z92401</t>
         </is>
       </c>
     </row>
@@ -567,7 +578,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA P M MIRANDA ESCOLA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA P M MIRANDA ESCOLA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>00000V64540</t>
         </is>
       </c>
     </row>
@@ -604,7 +620,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM MIRANDA ESC LUIZ RAIMUNDO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM MIRANDA ESC LUIZ RAIMUNDO RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>00000N08473</t>
         </is>
       </c>
     </row>
@@ -641,7 +662,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM MIRANDA ESC RURAL TUPA-BAE RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM MIRANDA ESC RURAL TUPA-BAE RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>00000V70445</t>
         </is>
       </c>
     </row>
@@ -678,7 +704,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM MIRANDA ESC RURAL INDIGENA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM MIRANDA ESC RURAL INDIGENA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>00000R24983</t>
         </is>
       </c>
     </row>
@@ -715,7 +746,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA P M MIRANDA ESCOLA IRMAOS SOUZA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA P M MIRANDA ESCOLA IRMAOS SOUZA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>00000U80390</t>
         </is>
       </c>
     </row>
@@ -752,7 +788,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM FMEC CASA DA CULTURA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM FMEC CASA DA CULTURA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>00000J47274</t>
         </is>
       </c>
     </row>
@@ -789,7 +830,12 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>TERENA DOMICÍLIO DE ENTREGA PMM SEC MUN DE TURISMO - CENTRO DE CULTURA TERENA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>TERENA DOMICÍLIO DE ENTREGA PMM SEC MUN DE TURISMO - CENTRO DE CULTURA TERENA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>00000C99922</t>
         </is>
       </c>
     </row>
@@ -826,7 +872,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>00000Z21172</t>
         </is>
       </c>
     </row>
@@ -863,7 +914,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUN ANEXO EMI PILAD REBUA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUN ANEXO EMI PILAD REBUA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>00000U16026</t>
         </is>
       </c>
     </row>
@@ -900,7 +956,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA DO MUNICIPIO DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA DO MUNICIPIO DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>00073000566</t>
         </is>
       </c>
     </row>
@@ -937,7 +998,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>BANDEIRANTES DOMICÍLIO DE ENTREGA PM DE MIRANDA ESCOLA ASSENTAMENTO BANDEIRANTES RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>BANDEIRANTES DOMICÍLIO DE ENTREGA PM DE MIRANDA ESCOLA ASSENTAMENTO BANDEIRANTES RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>00053112461</t>
         </is>
       </c>
     </row>
@@ -974,7 +1040,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM FMDCA CONSELHO TUTELAR RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM FMDCA CONSELHO TUTELAR RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>00000B82431</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1082,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM FUNDEB ESCOLA MUNC ROBERTO PAULO ALMEIDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM FUNDEB ESCOLA MUNC ROBERTO PAULO ALMEIDA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>00000J02389</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1124,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM SEC MUN DE OBRAS PARQUE INFANTIL DA COHAB RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM SEC MUN DE OBRAS PARQUE INFANTIL DA COHAB RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>00000K49812</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1166,12 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA ALDEIA CACHOEIRINHA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA ALDEIA CACHOEIRINHA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>00000N05865</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1208,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA ESCOLA INF ALDEIA CACHOEIRINHA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA ESCOLA INF ALDEIA CACHOEIRINHA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>00053043270</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1250,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA ALDEIA MORRINHO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA ALDEIA MORRINHO RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>00000V55056</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1292,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM MIRANDA BOMBA SALOBRA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM MIRANDA BOMBA SALOBRA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>00000R77299</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1334,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA ALDEIA BABACU RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA ALDEIA BABACU RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>00053112468</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1376,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM SEC MUN DE TURISMO FECIR RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM SEC MUN DE TURISMO FECIR RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>00000Z21381</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1418,12 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>ARGOLA DOMICÍLIO DE ENTREGA PM DE MIRANDA CENTRO DE INFORMATICA ALDEIA ARGOLA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>ARGOLA DOMICÍLIO DE ENTREGA PM DE MIRANDA CENTRO DE INFORMATICA ALDEIA ARGOLA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>00000V42618</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1460,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA MS RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA MS RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>00000K81154</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1502,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>FIGUEIREDO DOMICÍLIO DE ENTREGA PREFEITURA MUNIC MIRANDA ESCOLA PRES JOAO FIGUEIREDO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>FIGUEIREDO DOMICÍLIO DE ENTREGA PREFEITURA MUNIC MIRANDA ESCOLA PRES JOAO FIGUEIREDO RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>00000V60212</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1544,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>00073020959</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1586,12 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>00000Q93873</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1628,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>00000N52040</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1670,12 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>00000N12247</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1712,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>00000N71699</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1754,12 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>00000N66522</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1796,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA MUNICIPIO DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>D5108590614</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1838,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>00073036752</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1880,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>00000J29089</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1922,12 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>00000Q17539</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1964,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>00000Q17535</t>
         </is>
       </c>
     </row>
@@ -1825,7 +2006,12 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>00073022863</t>
         </is>
       </c>
     </row>
@@ -1862,7 +2048,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>00000V09251</t>
         </is>
       </c>
     </row>
@@ -1899,7 +2090,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>00000N06038</t>
         </is>
       </c>
     </row>
@@ -1936,7 +2132,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>00000R17730</t>
         </is>
       </c>
     </row>
@@ -1973,7 +2174,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>00000V26929</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2216,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA POSTO IND FUNAI RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA POSTO IND FUNAI RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>00000V26925</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2258,12 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREF MIRANDA/BOMBA MORRINHO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREF MIRANDA/BOMBA MORRINHO RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>00000V59743</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2300,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA P M MIRANDA ESC EXT JOSE BALBINO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA P M MIRANDA ESC EXT JOSE BALBINO RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>00033022316</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2342,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>00000F32304</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2384,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>00000F32303</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2426,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>00000P21671</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2468,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>00000V48617</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2510,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>00000P24711</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2552,12 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM POSTO TELEFONICO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM POSTO TELEFONICO RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>00033036400</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2594,12 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM FMS PSF BEIRA RIO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM FMS PSF BEIRA RIO RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>00000V59761</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2636,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM FMS SEC MUN DE SAUDE RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM FMS SEC MUN DE SAUDE RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>00000H35115</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2678,12 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM FMS PAB POSTO DE SAUDE CENTRAL RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM FMS PAB POSTO DE SAUDE CENTRAL RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>00000A75084</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2720,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM SEC MUNIC DE OBRAS GARAGEM RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM SEC MUNIC DE OBRAS GARAGEM RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>00000F66815</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2762,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM SEC MUN DE ESPORTES GINASIO DE ESPORTES RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM SEC MUN DE ESPORTES GINASIO DE ESPORTES RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>00000G63580</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2804,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>00073015734</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2846,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM ESCOLA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM ESCOLA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>00000A70570</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2888,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA DO MUNICIPIO DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA DO MUNICIPIO DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>00000N00069</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2930,12 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM FUNDEB ESCOLA MUNIC ESTANISLAU BOSSAY RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM FUNDEB ESCOLA MUNIC ESTANISLAU BOSSAY RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>00053008685</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2972,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM FMEC CRECHE MUN SAO FRANCISCO DE ASSIS RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM FMEC CRECHE MUN SAO FRANCISCO DE ASSIS RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>00000K51571</t>
         </is>
       </c>
     </row>
@@ -2713,7 +3014,12 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>00000F46786</t>
         </is>
       </c>
     </row>
@@ -2750,7 +3056,12 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM SEC MUN DE ESPORTES ESTADIO MUNICIPAL RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM SEC MUN DE ESPORTES ESTADIO MUNICIPAL RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>00000Z76767</t>
         </is>
       </c>
     </row>
@@ -2787,7 +3098,12 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM FUNDEB ESCOLA MUN MARIA DO ROSARIO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM FUNDEB ESCOLA MUN MARIA DO ROSARIO RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>00000J51404</t>
         </is>
       </c>
     </row>
@@ -2824,7 +3140,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA P M QUADRA DE ESPORTES RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA P M QUADRA DE ESPORTES RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>00073015696</t>
         </is>
       </c>
     </row>
@@ -2861,7 +3182,12 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM ESC ARTHEMIS P BOSSAY RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM ESC ARTHEMIS P BOSSAY RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>00053070405</t>
         </is>
       </c>
     </row>
@@ -2898,7 +3224,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM SEC MUN DE ADM CENTRO COMUNTARIO DA COHAB RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM SEC MUN DE ADM CENTRO COMUNTARIO DA COHAB RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>00000P31493</t>
         </is>
       </c>
     </row>
@@ -2935,7 +3266,12 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>TRABALHO DOMICÍLIO DE ENTREGA PMM FMAS SEC MUNIC DE ASSISTENCIA SOCIAL E TRABALHO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>TRABALHO DOMICÍLIO DE ENTREGA PMM FMAS SEC MUNIC DE ASSISTENCIA SOCIAL E TRABALHO RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>00000K81444</t>
         </is>
       </c>
     </row>
@@ -2972,7 +3308,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM FUNDEB ESCOLA MUNIC XV DE OUTUBRO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM FUNDEB ESCOLA MUNIC XV DE OUTUBRO RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>00000P28469</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3350,12 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM FMAS PETI RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM FMAS PETI RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>00000H35190</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3392,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>COHAB DOMICÍLIO DE ENTREGA PMM SEC MUN DE ESPORTES QUADRA DE ESPORTES DA COHAB RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>COHAB DOMICÍLIO DE ENTREGA PMM SEC MUN DE ESPORTES QUADRA DE ESPORTES DA COHAB RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>00000U90205</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3434,12 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM ESC GUMERCINDO RIBEIRO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM ESC GUMERCINDO RIBEIRO RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>00073008759</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3476,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM POCO SEMI ARTEZIANO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM POCO SEMI ARTEZIANO RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>00000V47586</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3518,12 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM POSTO TELEFONICO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM POSTO TELEFONICO RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>00000V68861</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3560,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>00000Z73066</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3602,12 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM SECRETARIA MUNICIPAL DE AGRICULTURA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM SECRETARIA MUNICIPAL DE AGRICULTURA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>00000Z90735</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3644,12 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM FMAS CASA ABRIGO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM FMAS CASA ABRIGO RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>00000F18289</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3686,12 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PMM FUNDEB ESCOLA MUNICIPAL ESTANISLAU BOSSAY RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PMM FUNDEB ESCOLA MUNICIPAL ESTANISLAU BOSSAY RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>00000A14485</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3728,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM BOMBA DE AGUA SALOBRA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM BOMBA DE AGUA SALOBRA RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>00000V86272</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3770,12 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM ESCOLA BALDOMERO CORTADA FILHO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM ESCOLA BALDOMERO CORTADA FILHO RUA TIRADENTES CENTRO, PACO MUNICIPAL CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>00053123196</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3812,12 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PM SECRETARIA DE TURISMO RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PM SECRETARIA DE TURISMO RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>00000Z64140</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3854,12 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+          <t>DOMICÍLIO DE ENTREGA PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL S/N CENTRO, PACO MUNICIPAL MIRANDA (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>00000A24607</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3896,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES CENTRO, PACO MUNICIPAL CEP: 79380000 MIRANDA MS (AG: 13)</t>
+          <t>PREFEITURA MUNICIPAL DE MIRANDA RUA TIRADENTES S/N CENTRO, PACO MUNICIPAL CEP: 79380000 MIRANDA MS (AG: 13)</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>00000Z73065</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:R82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3521,6 +3932,11 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3589,6 +4005,31 @@
           <t>JUL/21</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>AGO/21</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>SET/21</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OUT/21</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>NOV/21</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>DEZ/21</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3656,6 +4097,31 @@
           <t>615,00</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>1.230,00</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>1.948,00</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>1.845,00</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>1.845,00</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2.563,00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3723,6 +4189,31 @@
           <t>30,00</t>
         </is>
       </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3790,6 +4281,31 @@
           <t>94,00</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>83,00</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>78,00</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>82,00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3857,6 +4373,31 @@
           <t>30,00</t>
         </is>
       </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>116,00</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>111,00</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>103,00</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>97,00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3924,6 +4465,31 @@
           <t>119,00</t>
         </is>
       </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>382,00</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>136,00</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>134,00</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>220,00</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>159,00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -3991,6 +4557,31 @@
           <t>30,00</t>
         </is>
       </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>160,00</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>151,00</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>141,00</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>133,00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4058,6 +4649,31 @@
           <t>165,00</t>
         </is>
       </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>172,00</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>195,00</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>176,00</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>186,00</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>163,00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -4125,6 +4741,31 @@
           <t>430,00</t>
         </is>
       </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>380,00</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>380,00</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>390,00</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>230,00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4192,6 +4833,31 @@
           <t>0,00</t>
         </is>
       </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>80,00</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>80,00</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>80,00</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>160,00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4259,6 +4925,31 @@
           <t>64,00</t>
         </is>
       </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>58,00</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>56,00</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>58,00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -4326,6 +5017,31 @@
           <t>435,00</t>
         </is>
       </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>364,00</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>334,00</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1.912,00</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>505,00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4393,6 +5109,31 @@
           <t>63,00</t>
         </is>
       </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>50,00</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>61,00</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>61,00</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>50,00</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>60,00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4460,6 +5201,31 @@
           <t>270,00</t>
         </is>
       </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>306,00</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>608,00</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2.000,00</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>412,00</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>144,00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -4527,6 +5293,31 @@
           <t>144,00</t>
         </is>
       </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>151,00</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>431,00</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>1.496,00</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>763,00</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>1.896,00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4594,6 +5385,31 @@
           <t>171,00</t>
         </is>
       </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>188,00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>163,00</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>164,00</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>105,00</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>128,00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -4661,6 +5477,31 @@
           <t>733,00</t>
         </is>
       </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>659,00</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>638,00</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>682,00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4728,6 +5569,31 @@
           <t>74,00</t>
         </is>
       </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>517,00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>108,00</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>109,00</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>85,00</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>117,00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -4795,6 +5661,31 @@
           <t>177,00</t>
         </is>
       </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>50,00</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>153,00</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>144,00</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>50,00</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>152,00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4862,6 +5753,31 @@
           <t>948,00</t>
         </is>
       </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1.324,00</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>1.325,00</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1.263,00</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1.254,00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4929,6 +5845,31 @@
           <t>106,00</t>
         </is>
       </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>50,00</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>99,00</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>93,00</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>50,00</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>96,00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4996,6 +5937,31 @@
           <t>1.260,00</t>
         </is>
       </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1.560,00</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1.478,00</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>600,00</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1.020,00</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1.680,00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5063,6 +6029,31 @@
           <t>130,00</t>
         </is>
       </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>50,00</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>111,00</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>103,00</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>50,00</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>108,00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5130,6 +6121,31 @@
           <t>1.132,00</t>
         </is>
       </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1.015,00</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>1.213,00</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>1.279,00</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>1.314,00</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>1.208,00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -5197,6 +6213,31 @@
           <t>100,00</t>
         </is>
       </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>942,00</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>891,00</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>835,00</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>787,00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5264,6 +6305,31 @@
           <t>487,00</t>
         </is>
       </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>505,00</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>1.164,00</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1.431,00</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1.227,00</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1.511,00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -5331,6 +6397,31 @@
           <t>533,00</t>
         </is>
       </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>485,00</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>1.607,00</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>2.197,00</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>1.677,00</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>1.768,00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5398,6 +6489,31 @@
           <t>39,00</t>
         </is>
       </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>39,00</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>37,00</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>37,00</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>39,00</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>35,00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -5465,6 +6581,31 @@
           <t>31,00</t>
         </is>
       </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>37,00</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>41,00</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>41,00</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>41,00</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>38,00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5532,6 +6673,31 @@
           <t>18,00</t>
         </is>
       </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>15,00</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>16,00</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>16,00</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>16,00</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>14,00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -5599,6 +6765,31 @@
           <t>35,00</t>
         </is>
       </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>32,00</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>32,00</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>33,00</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>28,00</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>31,00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -5666,6 +6857,31 @@
           <t>40,00</t>
         </is>
       </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>34,00</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>35,00</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>36,00</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>35,00</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>32,00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -5733,6 +6949,31 @@
           <t>2.133,00</t>
         </is>
       </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>1.868,00</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>1.789,00</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>1.140,00</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>1.629,00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -5800,6 +7041,31 @@
           <t>68,00</t>
         </is>
       </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>74,00</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>267,00</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>387,00</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>449,00</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>575,00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -5867,6 +7133,31 @@
           <t>213,00</t>
         </is>
       </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>187,00</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>176,00</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>183,00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -5934,6 +7225,31 @@
           <t>907,00</t>
         </is>
       </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>714,00</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>884,00</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>876,00</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>1.003,00</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>897,00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -6001,6 +7317,31 @@
           <t>428,00</t>
         </is>
       </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>495,00</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>1.134,00</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>1.692,00</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>1.669,00</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>2.088,00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -6068,6 +7409,31 @@
           <t>196,00</t>
         </is>
       </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>197,00</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>71,00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>184,00</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>183,00</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>136,00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -6135,6 +7501,31 @@
           <t>370,00</t>
         </is>
       </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>676,00</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>1.078,00</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>388,00</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>1.500,00</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>1.380,00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -6202,6 +7593,31 @@
           <t>117,00</t>
         </is>
       </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>185,00</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>353,00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>452,00</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>445,00</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>441,00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -6269,6 +7685,31 @@
           <t>78,00</t>
         </is>
       </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>74,00</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>64,00</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>70,00</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>131,00</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>67,00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -6336,6 +7777,31 @@
           <t>289,00</t>
         </is>
       </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>50,00</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>249,00</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>234,00</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>50,00</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>237,00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -6403,6 +7869,31 @@
           <t>100,00</t>
         </is>
       </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -6470,6 +7961,31 @@
           <t>95,00</t>
         </is>
       </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>101,00</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>91,00</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>150,00</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>106,00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -6537,6 +8053,31 @@
           <t>86,00</t>
         </is>
       </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>111,00</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>189,00</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>211,00</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>268,00</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>358,00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -6604,6 +8145,31 @@
           <t>78,00</t>
         </is>
       </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>86,00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>126,00</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>129,00</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>198,00</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>278,00</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -6671,6 +8237,31 @@
           <t>176,00</t>
         </is>
       </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>257,00</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>370,00</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>362,00</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>630,00</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>1.038,00</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -6738,6 +8329,31 @@
           <t>288,00</t>
         </is>
       </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>528,00</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>1.063,00</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>962,00</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>1.094,00</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>1.236,00</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -6805,6 +8421,31 @@
           <t>79,00</t>
         </is>
       </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>118,00</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>319,00</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>337,00</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>309,00</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>295,00</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -6872,6 +8513,31 @@
           <t>30,00</t>
         </is>
       </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -6939,6 +8605,31 @@
           <t>0,00</t>
         </is>
       </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>129,00</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>132,00</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>134,00</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -7006,6 +8697,31 @@
           <t>10,00</t>
         </is>
       </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>50,00</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>640,00</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>620,00</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>860,00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -7073,6 +8789,31 @@
           <t>1.415,00</t>
         </is>
       </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>1.351,00</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>3.307,00</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>4.897,00</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>3.490,00</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>5.946,00</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -7140,6 +8881,31 @@
           <t>584,00</t>
         </is>
       </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>588,00</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>736,00</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>874,00</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>1.014,00</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>1.296,00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -7207,6 +8973,31 @@
           <t>1.021,00</t>
         </is>
       </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>1.458,00</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>1.557,00</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>1.601,00</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>1.828,00</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>1.464,00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -7274,6 +9065,31 @@
           <t>1.378,00</t>
         </is>
       </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>2.237,00</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>3.876,00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>4.221,00</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>4.443,00</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>4.511,00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -7341,6 +9157,31 @@
           <t>144,00</t>
         </is>
       </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>141,00</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>137,00</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>134,00</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>174,00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -7408,6 +9249,31 @@
           <t>237,00</t>
         </is>
       </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>198,00</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>312,00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>389,00</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>364,00</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>531,00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -7475,6 +9341,31 @@
           <t>52,00</t>
         </is>
       </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>141,00</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>114,00</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>189,00</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>582,00</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>1.041,00</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -7542,6 +9433,31 @@
           <t>205,00</t>
         </is>
       </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>222,00</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>525,00</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>705,00</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>1.935,00</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>2.304,00</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -7609,6 +9525,31 @@
           <t>2.628,00</t>
         </is>
       </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>2.923,00</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>2.490,00</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>2.780,00</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>3.577,00</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>3.817,00</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -7676,6 +9617,31 @@
           <t>1.320,00</t>
         </is>
       </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>1.840,00</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>1.680,00</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>1.600,00</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>1.720,00</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>1.520,00</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -7743,6 +9709,31 @@
           <t>249,00</t>
         </is>
       </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>226,00</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>476,00</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>797,00</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>864,00</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>1.645,00</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -7810,6 +9801,31 @@
           <t>1.840,00</t>
         </is>
       </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>2.988,00</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>1.893,00</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>1.883,00</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>1.100,00</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>1.909,00</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -7877,6 +9893,31 @@
           <t>186,00</t>
         </is>
       </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>50,00</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>155,00</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>143,00</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>50,00</t>
+        </is>
+      </c>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>151,00</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -7944,6 +9985,31 @@
           <t>0,00</t>
         </is>
       </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -8011,6 +10077,31 @@
           <t>543,00</t>
         </is>
       </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>584,00</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>1.180,00</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>1.346,00</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr">
+        <is>
+          <t>988,00</t>
+        </is>
+      </c>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>1.408,00</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -8078,6 +10169,31 @@
           <t>285,00</t>
         </is>
       </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>387,00</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>670,00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>715,00</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>2.387,00</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>1.749,00</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -8145,6 +10261,31 @@
           <t>290,00</t>
         </is>
       </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>330,00</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>640,00</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>1.040,00</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>750,00</t>
+        </is>
+      </c>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>1.600,00</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -8212,6 +10353,31 @@
           <t>25,00</t>
         </is>
       </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>92,00</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>93,00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>103,00</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>375,00</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>147,00</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -8279,6 +10445,31 @@
           <t>100,00</t>
         </is>
       </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>145,00</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>141,00</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>100,00</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr">
+        <is>
+          <t>138,00</t>
+        </is>
+      </c>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>135,00</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -8346,6 +10537,31 @@
           <t>591,00</t>
         </is>
       </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>589,00</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>614,00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>590,00</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>588,00</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>585,00</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -8413,6 +10629,31 @@
           <t>30,00</t>
         </is>
       </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="R73" s="3" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -8480,6 +10721,31 @@
           <t>2.358,00</t>
         </is>
       </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>2.749,00</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>5.091,00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>6.180,00</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>6.251,00</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>6.130,00</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -8547,6 +10813,31 @@
           <t>420,00</t>
         </is>
       </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>480,00</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>420,00</t>
+        </is>
+      </c>
+      <c r="Q75" s="3" t="inlineStr">
+        <is>
+          <t>300,00</t>
+        </is>
+      </c>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>540,00</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -8614,6 +10905,31 @@
           <t>484,00</t>
         </is>
       </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>529,00</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>860,00</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>1.247,00</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>1.088,00</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>827,00</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -8681,6 +10997,31 @@
           <t>240,00</t>
         </is>
       </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>410,00</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>990,00</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>1.040,00</t>
+        </is>
+      </c>
+      <c r="Q77" s="3" t="inlineStr">
+        <is>
+          <t>1.600,00</t>
+        </is>
+      </c>
+      <c r="R77" s="3" t="inlineStr">
+        <is>
+          <t>1.870,00</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -8748,6 +11089,31 @@
           <t>931,00</t>
         </is>
       </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>837,00</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>835,00</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>738,00</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>863,00</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>866,00</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -8815,6 +11181,31 @@
           <t>180,00</t>
         </is>
       </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>86,00</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>173,00</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>163,00</t>
+        </is>
+      </c>
+      <c r="Q79" s="3" t="inlineStr">
+        <is>
+          <t>268,00</t>
+        </is>
+      </c>
+      <c r="R79" s="3" t="inlineStr">
+        <is>
+          <t>170,00</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -8882,6 +11273,31 @@
           <t>1.000,00</t>
         </is>
       </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>920,00</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>1.120,00</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>1.160,00</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>1.160,00</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>1.080,00</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -8949,6 +11365,31 @@
           <t>160,00</t>
         </is>
       </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
+          <t>300,00</t>
+        </is>
+      </c>
+      <c r="O81" s="3" t="inlineStr">
+        <is>
+          <t>710,00</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>560,00</t>
+        </is>
+      </c>
+      <c r="Q81" s="3" t="inlineStr">
+        <is>
+          <t>760,00</t>
+        </is>
+      </c>
+      <c r="R81" s="3" t="inlineStr">
+        <is>
+          <t>750,00</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -9014,6 +11455,31 @@
       <c r="M82" s="2" t="inlineStr">
         <is>
           <t>103,00</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>103,00</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>308,00</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>308,00</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>308,00</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>410,00</t>
         </is>
       </c>
     </row>
